--- a/data/trans_camb/P12_2_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 1,9</t>
+          <t>-6,36; 1,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 4,0</t>
+          <t>-4,74; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 6,6</t>
+          <t>-1,54; 6,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 0,43</t>
+          <t>-9,62; 0,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -2,35</t>
+          <t>-11,82; -2,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; -2,06</t>
+          <t>-10,51; -1,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -0,5</t>
+          <t>-6,55; -0,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; -0,7</t>
+          <t>-6,82; -0,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 1,15</t>
+          <t>-4,96; 0,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 11,36</t>
+          <t>-31,14; 10,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 25,99</t>
+          <t>-23,54; 22,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 40,48</t>
+          <t>-6,64; 38,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 2,28</t>
+          <t>-29,43; 0,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,26; -8,44</t>
+          <t>-36,89; -8,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,8; -7,27</t>
+          <t>-32,33; -6,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,71; -2,06</t>
+          <t>-25,32; -0,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,0; -2,94</t>
+          <t>-27,2; -1,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 5,12</t>
+          <t>-19,26; 4,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; -3,74</t>
+          <t>-10,48; -3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,61; -3,4</t>
+          <t>-10,29; -3,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,96; -6,58</t>
+          <t>-17,77; -6,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -6,3</t>
+          <t>-14,4; -5,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,54; -6,04</t>
+          <t>-14,74; -6,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,5; -8,03</t>
+          <t>-15,63; -8,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -6,27</t>
+          <t>-11,4; -5,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -5,93</t>
+          <t>-11,11; -5,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,51; -8,93</t>
+          <t>-17,9; -8,94</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,4; -19,02</t>
+          <t>-45,18; -18,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,1; -17,71</t>
+          <t>-44,53; -17,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,5; -33,16</t>
+          <t>-76,8; -32,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,98; -20,41</t>
+          <t>-40,74; -19,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,87; -18,93</t>
+          <t>-41,78; -19,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,9; -26,47</t>
+          <t>-43,74; -26,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -23,66</t>
+          <t>-40,25; -21,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -23,1</t>
+          <t>-38,81; -23,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -34,03</t>
+          <t>-62,58; -33,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,03</t>
+          <t>-3,21; 5,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,02</t>
+          <t>-6,05; 2,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 2,18</t>
+          <t>-6,09; 2,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 5,59</t>
+          <t>-3,92; 5,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 0,76</t>
+          <t>-8,28; 0,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,53; -0,55</t>
+          <t>-16,82; -0,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,88</t>
+          <t>-1,85; 4,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,28</t>
+          <t>-5,61; 0,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,12; -0,56</t>
+          <t>-10,6; -0,3</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 32,23</t>
+          <t>-17,67; 41,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,07; 13,61</t>
+          <t>-31,73; 14,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 14,11</t>
+          <t>-30,89; 16,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 26,56</t>
+          <t>-14,63; 23,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 3,23</t>
+          <t>-31,37; 4,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,9; -2,46</t>
+          <t>-66,34; -2,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 20,42</t>
+          <t>-8,59; 21,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 2,02</t>
+          <t>-25,84; 0,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,67; -3,46</t>
+          <t>-49,02; -2,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 4,12</t>
+          <t>-3,25; 4,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -0,82</t>
+          <t>-7,92; -0,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,12</t>
+          <t>-4,32; 3,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,08</t>
+          <t>-5,66; 2,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,36; -3,57</t>
+          <t>-10,91; -3,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,41; -2,25</t>
+          <t>-11,37; -1,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,02</t>
+          <t>-3,47; 1,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -3,11</t>
+          <t>-8,78; -3,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -0,35</t>
+          <t>-6,65; -0,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 22,18</t>
+          <t>-14,59; 25,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,0; -3,37</t>
+          <t>-35,95; -3,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 16,73</t>
+          <t>-19,67; 17,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 11,03</t>
+          <t>-17,23; 8,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,85; -12,45</t>
+          <t>-33,79; -11,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,26; -8,21</t>
+          <t>-35,96; -7,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 8,41</t>
+          <t>-12,86; 7,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -12,24</t>
+          <t>-32,18; -14,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,4; -1,97</t>
+          <t>-24,52; -2,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,38</t>
+          <t>-4,04; -0,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,84</t>
+          <t>-5,67; -2,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -1,68</t>
+          <t>-7,08; -1,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -2,09</t>
+          <t>-6,44; -2,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -5,27</t>
+          <t>-9,75; -5,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,64; -5,64</t>
+          <t>-12,25; -5,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -1,68</t>
+          <t>-4,66; -1,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -4,05</t>
+          <t>-7,15; -4,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -4,11</t>
+          <t>-8,26; -3,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -2,06</t>
+          <t>-20,0; -1,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,63; -9,85</t>
+          <t>-27,6; -11,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -8,84</t>
+          <t>-36,18; -8,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,78; -7,32</t>
+          <t>-20,95; -7,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,2; -18,31</t>
+          <t>-31,61; -18,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,08; -19,56</t>
+          <t>-40,38; -19,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,15; -6,93</t>
+          <t>-18,28; -7,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,67; -16,88</t>
+          <t>-28,02; -17,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,82; -17,27</t>
+          <t>-33,13; -16,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_2_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P12_2_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,17</t>
+          <t>-6,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,93</t>
+          <t>-2,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 1,78</t>
+          <t>-6,19; 2,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 3,56</t>
+          <t>-4,34; 3,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 6,18</t>
+          <t>-2,44; 6,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,07</t>
+          <t>-9,29; 0,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -2,42</t>
+          <t>-11,86; -2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -1,75</t>
+          <t>-10,5; -1,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -0,2</t>
+          <t>-6,72; -0,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -0,41</t>
+          <t>-6,94; -0,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,97</t>
+          <t>-4,83; 1,08</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-20,98%</t>
+          <t>-21,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-8,1%</t>
+          <t>-8,65%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 10,46</t>
+          <t>-29,99; 12,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 22,23</t>
+          <t>-21,73; 23,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 38,23</t>
+          <t>-11,48; 37,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 0,27</t>
+          <t>-29,08; 0,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,89; -8,82</t>
+          <t>-37,34; -8,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,33; -6,29</t>
+          <t>-32,61; -7,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,32; -0,83</t>
+          <t>-26,58; -1,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,2; -1,79</t>
+          <t>-26,87; -3,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,26; 4,47</t>
+          <t>-18,93; 5,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,86</t>
+          <t>-7,98</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,73</t>
+          <t>-11,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,9</t>
+          <t>-9,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,48; -3,59</t>
+          <t>-10,36; -3,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,29; -3,27</t>
+          <t>-10,67; -3,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -6,56</t>
+          <t>-11,66; -4,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -5,91</t>
+          <t>-14,32; -5,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,74; -6,14</t>
+          <t>-14,65; -6,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,63; -8,23</t>
+          <t>-15,48; -8,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -5,58</t>
+          <t>-11,26; -5,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -5,98</t>
+          <t>-11,23; -5,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,9; -8,94</t>
+          <t>-12,59; -7,52</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-50,34%</t>
+          <t>-37,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-35,44%</t>
+          <t>-36,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,5%</t>
+          <t>-36,35%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,18; -18,32</t>
+          <t>-44,39; -17,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,53; -17,09</t>
+          <t>-45,05; -18,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,8; -32,66</t>
+          <t>-49,15; -23,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,74; -19,2</t>
+          <t>-40,55; -19,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,78; -19,8</t>
+          <t>-41,24; -20,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,74; -26,39</t>
+          <t>-44,05; -26,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,25; -21,89</t>
+          <t>-39,41; -22,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,81; -23,16</t>
+          <t>-39,58; -22,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,58; -33,89</t>
+          <t>-43,68; -28,45</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-6,72</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-0,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 5,96</t>
+          <t>-3,19; 5,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 2,02</t>
+          <t>-5,97; 2,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 2,51</t>
+          <t>-5,65; 2,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 5,11</t>
+          <t>-3,26; 5,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 0,9</t>
+          <t>-7,42; 0,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,82; -0,62</t>
+          <t>-3,84; 4,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,03</t>
+          <t>-2,39; 4,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,17</t>
+          <t>-5,91; 0,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -0,3</t>
+          <t>-3,57; 2,43</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-10,43%</t>
+          <t>-8,93%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-28,53%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-20,45%</t>
+          <t>-2,48%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 41,49</t>
+          <t>-16,65; 34,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 14,86</t>
+          <t>-30,78; 13,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 16,65</t>
+          <t>-29,26; 18,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 23,62</t>
+          <t>-12,81; 25,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 4,54</t>
+          <t>-29,29; 4,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,34; -2,81</t>
+          <t>-14,75; 20,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 21,65</t>
+          <t>-10,79; 22,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,84; 0,91</t>
+          <t>-26,54; 1,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,02; -2,03</t>
+          <t>-16,49; 13,14</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-5,08</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,44</t>
+          <t>-3,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 4,66</t>
+          <t>-2,88; 4,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -0,78</t>
+          <t>-7,73; -0,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,09</t>
+          <t>-4,35; 2,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 2,43</t>
+          <t>-5,68; 2,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,91; -3,42</t>
+          <t>-11,03; -3,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -1,96</t>
+          <t>-8,74; -1,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,93</t>
+          <t>-3,6; 2,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,78; -3,44</t>
+          <t>-8,66; -3,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -0,62</t>
+          <t>-5,8; -0,71</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-3,44%</t>
+          <t>-5,08%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,92%</t>
+          <t>-16,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,44%</t>
+          <t>-12,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 25,78</t>
+          <t>-13,26; 24,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,95; -3,93</t>
+          <t>-35,63; -4,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 17,15</t>
+          <t>-20,14; 16,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 8,97</t>
+          <t>-17,04; 8,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,79; -11,99</t>
+          <t>-33,66; -11,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,96; -7,33</t>
+          <t>-26,49; -5,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 7,88</t>
+          <t>-13,2; 8,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,18; -14,14</t>
+          <t>-32,1; -13,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -2,51</t>
+          <t>-21,43; -3,12</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,75</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,16</t>
+          <t>-6,17</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-4,39</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; -0,2</t>
+          <t>-4,08; -0,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -2,05</t>
+          <t>-5,49; -2,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -1,59</t>
+          <t>-4,47; -0,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -2,09</t>
+          <t>-6,3; -1,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -5,35</t>
+          <t>-9,5; -5,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -5,71</t>
+          <t>-8,29; -4,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -1,7</t>
+          <t>-4,82; -1,8</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -4,23</t>
+          <t>-7,12; -4,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,26; -3,95</t>
+          <t>-5,77; -3,06</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-19,23%</t>
+          <t>-13,47%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,5%</t>
+          <t>-20,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,13%</t>
+          <t>-17,78%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -1,33</t>
+          <t>-20,14; -1,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,6; -11,07</t>
+          <t>-27,15; -11,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,18; -8,34</t>
+          <t>-21,9; -4,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,95; -7,27</t>
+          <t>-20,44; -6,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -18,72</t>
+          <t>-31,14; -18,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-40,38; -19,91</t>
+          <t>-26,83; -15,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -7,1</t>
+          <t>-18,88; -7,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -17,69</t>
+          <t>-27,94; -17,02</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,13; -16,58</t>
+          <t>-22,62; -12,89</t>
         </is>
       </c>
     </row>
